--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.15637345974978</v>
+        <v>5.550410687209339</v>
       </c>
       <c r="D2" t="n">
-        <v>36.09221698320974</v>
+        <v>5.864985259771583</v>
       </c>
       <c r="E2" t="n">
-        <v>13.56521476065618</v>
+        <v>2.204347398606629</v>
       </c>
       <c r="F2" t="n">
-        <v>13.01619954030927</v>
+        <v>2.115132425300255</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>67.29425557699284</v>
+        <v>10.93531653126134</v>
       </c>
       <c r="D3" t="n">
-        <v>67.89589878787956</v>
+        <v>11.03308355303043</v>
       </c>
       <c r="E3" t="n">
-        <v>13.56521476065618</v>
+        <v>2.204347398606629</v>
       </c>
       <c r="F3" t="n">
-        <v>13.01619954030927</v>
+        <v>2.115132425300255</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.60911312199239</v>
+        <v>7.898980882323763</v>
       </c>
       <c r="D4" t="n">
-        <v>50.04703583131734</v>
+        <v>8.132643322589068</v>
       </c>
       <c r="E4" t="n">
-        <v>13.56521476065618</v>
+        <v>2.204347398606629</v>
       </c>
       <c r="F4" t="n">
-        <v>13.01619954030927</v>
+        <v>2.115132425300255</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
